--- a/Assets/Game/Content/Data/CharacterTable.xlsx
+++ b/Assets/Game/Content/Data/CharacterTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlier\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlierNew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A55C43-25D4-4DD5-A290-4B2C50426D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7460F8B9-6146-48C8-9964-EECA62815792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -201,7 +201,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,17 +531,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="19.3984375" customWidth="1"/>
-    <col min="4" max="4" width="26.3984375" customWidth="1"/>
-    <col min="5" max="5" width="11.3984375" customWidth="1"/>
+    <col min="2" max="3" width="19.44140625" customWidth="1"/>
+    <col min="4" max="4" width="26.44140625" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="16.3984375" customWidth="1"/>
-    <col min="8" max="8" width="65.59765625" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -567,7 +567,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -593,7 +593,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -614,7 +614,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -634,7 +634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -652,7 +652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
@@ -678,7 +678,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>33</v>
       </c>
@@ -704,7 +704,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>44</v>
       </c>
@@ -730,7 +730,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>39</v>
       </c>

--- a/Assets/Game/Content/Data/CharacterTable.xlsx
+++ b/Assets/Game/Content/Data/CharacterTable.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlierNew\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7460F8B9-6146-48C8-9964-EECA62815792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDEABEE-7D3E-4626-8B8D-B9195F41C8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>Id</t>
   </si>
@@ -162,9 +162,6 @@
     <t>[8,8,0,0]</t>
   </si>
   <si>
-    <t>[F100,F100,W100,W100,F101,W101,F103,FW100,F111,FW102]</t>
-  </si>
-  <si>
     <t>Earth</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -194,6 +191,34 @@
   </si>
   <si>
     <t>[false,false,false,false]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Air</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character_Airbender</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character_Airbender_Desc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[false,false, false, true]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,0,0,3]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[A100,A100,A100,A101,A101,A101,A102,A103]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[F100,W100,F101,W101,F103,FW100,F111,FW102]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -530,15 +555,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="19.44140625" customWidth="1"/>
-    <col min="4" max="4" width="26.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" customWidth="1"/>
+    <col min="2" max="3" width="19.3984375" customWidth="1"/>
+    <col min="4" max="4" width="26.3984375" customWidth="1"/>
+    <col min="5" max="5" width="11.3984375" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="16.44140625" customWidth="1"/>
-    <col min="8" max="8" width="65.5546875" customWidth="1"/>
+    <col min="7" max="7" width="16.3984375" customWidth="1"/>
+    <col min="8" max="8" width="65.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -645,7 +670,7 @@
         <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1"/>
       <c r="G5">
@@ -706,19 +731,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -727,33 +752,59 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>43</v>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Game/Content/Data/CharacterTable.xlsx
+++ b/Assets/Game/Content/Data/CharacterTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDEABEE-7D3E-4626-8B8D-B9195F41C8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C88B96-A359-4D86-B3BF-4A334432A795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -182,10 +182,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>[E100,E100,E100,E101,E101,E101,E102,E103]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>[true,true, false, false]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -219,6 +215,10 @@
   </si>
   <si>
     <t>[F100,W100,F101,W101,F103,FW100,F111,FW102]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[E100,E100,E100,E100,E101,E101,E102,E103]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -238,6 +238,8 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -282,7 +284,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -558,12 +560,12 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="19.3984375" customWidth="1"/>
-    <col min="4" max="4" width="26.3984375" customWidth="1"/>
-    <col min="5" max="5" width="11.3984375" customWidth="1"/>
+    <col min="2" max="3" width="19.44140625" customWidth="1"/>
+    <col min="4" max="4" width="26.44140625" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="16.3984375" customWidth="1"/>
-    <col min="8" max="8" width="65.59765625" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -670,7 +672,7 @@
         <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" s="1"/>
       <c r="G5">
@@ -752,33 +754,33 @@
         <v>5</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -792,7 +794,7 @@
         <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>42</v>
@@ -804,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
